--- a/docs/parameter-hallucination/shortcut-gap-reanalysis/devapp/devapp_cli_param_hallucination_analysis.xlsx
+++ b/docs/parameter-hallucination/shortcut-gap-reanalysis/devapp/devapp_cli_param_hallucination_analysis.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇报总览" sheetId="1" r:id="Rebf2b199ae294ce6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数问题明细" sheetId="2" r:id="R73c18f48c185429c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="兜底解决方案" sheetId="3" r:id="Rb1f6715250734510"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前无法解决" sheetId="4" r:id="Rfdd697234cf143d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分析依据" sheetId="5" r:id="R064f2cc9e6ac4072"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇报总览" sheetId="1" r:id="R71c87bfb70744e63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数问题明细" sheetId="2" r:id="R6e5acfbd007c4a20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="兜底解决方案" sheetId="3" r:id="R5b83e83f75cf45c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前无法解决" sheetId="4" r:id="R98eb9c08796747a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分析依据" sheetId="5" r:id="R43ed1744b1804714"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -532,7 +532,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>冻结基线 5f906bf8b61bc54a75f6c2b46219a1deb682b600｜正式别名表未修改｜候选、报告、五页工作簿独立交付</x:v>
+        <x:v>冻结基线 f4474b57eb1db23b1638b9574be2f5dca368a360｜正式别名表未修改｜候选、报告、五页工作簿独立交付</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -592,7 +592,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="56" t="str">
-        <x:v>结论：候选变更 4 个 concept、6 个 command override、22 条 fixture；逐产品生成与政策门禁均通过。</x:v>
+        <x:v>结论：候选变更 4 个 concept、6 个 command override、24 条 fixture；逐产品生成与政策门禁均通过。</x:v>
       </x:c>
       <x:c r="B8" s="57"/>
       <x:c r="C8" s="57"/>
@@ -762,7 +762,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>冻结基线 5f906bf8b61bc54a75f6c2b46219a1deb682b600｜逐命令核对真实 Help/Cobra、运行时 Schema、Skill 与正式别名表</x:v>
+        <x:v>冻结基线 f4474b57eb1db23b1638b9574be2f5dca368a360｜逐命令核对真实 Help/Cobra、运行时 Schema、Skill 与正式别名表</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -828,10 +828,10 @@
         <x:v>unified-app-id,name,brief,desc,icon-media-id,outgoing-url,event-callback-url,mode,skills</x:v>
       </x:c>
       <x:c r="D6" s="19" t="str">
-        <x:v>两个回调 URL、机器人名称、简介/描述、mediaId 角色并存</x:v>
+        <x:v>两个回调 URL、机器人名称、简介/描述、mediaId 与技能 ID 列表角色并存</x:v>
       </x:c>
       <x:c r="E6" s="19" t="str">
-        <x:v>复用必要 concept；仅角色完整 URL 别名；generic callback-url 歧义</x:v>
+        <x:v>复用必要 concept；skill-list 保留 ID 列表原值，skill-names 保持歧义；仅角色完整 URL 别名</x:v>
       </x:c>
       <x:c r="F6" s="19" t="str">
         <x:v>部分兜底</x:v>
@@ -967,7 +967,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>仅接受同实体、同角色、同值域、同基数且值原样传递的映射；共新增 22 条 fixture</x:v>
+        <x:v>仅接受同实体、同角色、同值域、同基数且值原样传递的映射；共新增 24 条 fixture</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -1128,7 +1128,7 @@
         <x:v>devapp +robot-config</x:v>
       </x:c>
       <x:c r="C10" s="19" t="str">
-        <x:v>bind 3 / alias 10 / block 4 / ambiguous 4</x:v>
+        <x:v>bind 3 / alias 9 / block 4 / ambiguous 5</x:v>
       </x:c>
       <x:c r="D10" s="19" t="str">
         <x:v>devapp +robot-config</x:v>
@@ -1137,7 +1137,7 @@
         <x:v>仅在本命令启用已验证的 bind / scoped alias；其余近似参数保持拦截或歧义保护</x:v>
       </x:c>
       <x:c r="F10" s="19" t="str">
-        <x:v>preview-media-id, file-id, app-key, agent-id, callback-url, url, summary, id</x:v>
+        <x:v>preview-media-id, file-id, app-key, agent-id, callback-url, url, summary, id, skill-names</x:v>
       </x:c>
       <x:c r="G10" s="19" t="str">
         <x:v>严格命令域</x:v>
@@ -1324,13 +1324,13 @@
         <x:v>devapp +robot-config</x:v>
       </x:c>
       <x:c r="C6" s="19" t="str">
-        <x:v>两个回调 URL、机器人名称、简介/描述、mediaId 角色并存</x:v>
+        <x:v>两个回调 URL、机器人名称、简介/描述、mediaId 与技能 ID 列表角色并存</x:v>
       </x:c>
       <x:c r="D6" s="19" t="str">
         <x:v>部分兜底</x:v>
       </x:c>
       <x:c r="E6" s="19" t="str">
-        <x:v>复用必要 concept；仅角色完整 URL 别名；generic callback-url 歧义</x:v>
+        <x:v>skill-list 仅保留 ID 列表原值；skill-names 与 generic callback-url 保持歧义；错误 media/app ID 域阻断</x:v>
       </x:c>
       <x:c r="F6" s="19" t="str">
         <x:v>需修改真实 CLI/框架，或由 Agent 明确选择真实参数；别名表不做查找、转换、枚举翻译或基数变化</x:v>
@@ -1470,7 +1470,7 @@
         <x:v>冻结基线</x:v>
       </x:c>
       <x:c r="B5" s="18" t="str">
-        <x:v>origin/main@5f906bf8b61bc54a75f6c2b46219a1deb682b600</x:v>
+        <x:v>origin/main@f4474b57eb1db23b1638b9574be2f5dca368a360</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
         <x:v>通过</x:v>
@@ -1546,7 +1546,7 @@
         <x:v>已补齐</x:v>
       </x:c>
       <x:c r="D10" s="19" t="str">
-        <x:v>candidate-only；未启用候选时不扩大既有 activeCommands</x:v>
+        <x:v>candidate-only；robot-config 模板显式携带 --skills；未启用候选时不扩大既有 activeCommands</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
